--- a/artfynd/A 5790-2025 artfynd.xlsx
+++ b/artfynd/A 5790-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123046023</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5790-2025 artfynd.xlsx
+++ b/artfynd/A 5790-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123046023</v>
       </c>
       <c r="B2" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5790-2025 artfynd.xlsx
+++ b/artfynd/A 5790-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123046023</v>
       </c>
       <c r="B2" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5790-2025 artfynd.xlsx
+++ b/artfynd/A 5790-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123046023</v>
       </c>
       <c r="B2" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5790-2025 artfynd.xlsx
+++ b/artfynd/A 5790-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123046023</v>
       </c>
       <c r="B2" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
